--- a/data/transcripts/Int_Codes.xlsx
+++ b/data/transcripts/Int_Codes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JoeWe\IndProj\Project\data\transcripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55098F65-6AB6-44BD-9767-02409413F41A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4EC3CB3-896E-4539-B201-37ED92CB5417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2206,6 +2206,9 @@
       <c r="A104" s="4" t="s">
         <v>133</v>
       </c>
+      <c r="B104">
+        <v>13</v>
+      </c>
       <c r="C104" t="s">
         <v>20</v>
       </c>
@@ -2214,6 +2217,9 @@
       <c r="A105" s="4" t="s">
         <v>134</v>
       </c>
+      <c r="B105">
+        <v>13</v>
+      </c>
       <c r="C105" t="s">
         <v>109</v>
       </c>
@@ -2222,6 +2228,9 @@
       <c r="A106" s="4" t="s">
         <v>135</v>
       </c>
+      <c r="B106">
+        <v>13</v>
+      </c>
       <c r="C106" t="s">
         <v>31</v>
       </c>
@@ -2230,6 +2239,9 @@
       <c r="A107" s="4" t="s">
         <v>136</v>
       </c>
+      <c r="B107">
+        <v>13</v>
+      </c>
       <c r="C107" t="s">
         <v>15</v>
       </c>
@@ -2238,6 +2250,9 @@
       <c r="A108" s="4" t="s">
         <v>137</v>
       </c>
+      <c r="B108">
+        <v>13</v>
+      </c>
       <c r="C108" t="s">
         <v>11</v>
       </c>
@@ -2246,6 +2261,9 @@
       <c r="A109" s="4" t="s">
         <v>139</v>
       </c>
+      <c r="B109">
+        <v>13</v>
+      </c>
       <c r="C109" t="s">
         <v>70</v>
       </c>
@@ -2254,6 +2272,9 @@
       <c r="A110" s="4" t="s">
         <v>140</v>
       </c>
+      <c r="B110">
+        <v>13</v>
+      </c>
       <c r="C110" t="s">
         <v>70</v>
       </c>
@@ -2262,6 +2283,9 @@
       <c r="A111" s="4" t="s">
         <v>141</v>
       </c>
+      <c r="B111">
+        <v>13</v>
+      </c>
       <c r="C111" t="s">
         <v>5</v>
       </c>
@@ -2269,6 +2293,9 @@
     <row r="112" spans="1:3" ht="156.75" x14ac:dyDescent="0.45">
       <c r="A112" s="4" t="s">
         <v>142</v>
+      </c>
+      <c r="B112">
+        <v>13</v>
       </c>
       <c r="C112" t="s">
         <v>10</v>

--- a/data/transcripts/Int_Codes.xlsx
+++ b/data/transcripts/Int_Codes.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JoeWe\IndProj\Project\data\transcripts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JoeWe\Uni\IndProject\Project\data\transcripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4EC3CB3-896E-4539-B201-37ED92CB5417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA10CB26-2F83-491B-B702-38D0FA2733AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quotes" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="143">
   <si>
     <t>Quote</t>
   </si>
@@ -432,11 +432,6 @@
     <t>See if I can, like, pinpoint visualisation to pick up my name cues. Then yeah, probably.</t>
   </si>
   <si>
-    <t xml:space="preserve">
-So, I think it's because I'm more familiar with the radar.
-So, like, in video games, they use the radar, so, yeah, and I play a lot of video games, so I'm more familiar with it.</t>
-  </si>
-  <si>
     <t>Yeah, but the arrow I feel it's too overwhelming.
 Yeah, it occupies too much space and the lights, I think it's too minimal.</t>
   </si>
@@ -719,6 +714,10 @@
     <t>Like, I don't, like, I think as it is, it's fine because it would just, I'm hoping it would just be like, okay, then the light will show up or something, but like some kind of notification to say like, oh, it's picking up, I don't know, maybe if there's like a little image that goes, I don't know, you choose your own image.
 Yeah.
 Once it picks up that sound because it stands for your name. You see it pop up and you know which direction it's coming from.</t>
+  </si>
+  <si>
+    <t>So, I think it's because I'm more familiar with the radar.
+So, like, in video games, they use the radar, so, yeah, and I play a lot of video games, so I'm more familiar with it.</t>
   </si>
 </sst>
 </file>
@@ -1058,15 +1057,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D125"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:D112"/>
+  <sheetFormatPr defaultRowHeight="93" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="51.06640625" customWidth="1"/>
-    <col min="2" max="2" width="28.46484375" customWidth="1"/>
-    <col min="3" max="3" width="44.1328125" customWidth="1"/>
+    <col min="1" max="1" width="51" customWidth="1"/>
+    <col min="2" max="2" width="28.42578125" customWidth="1"/>
+    <col min="3" max="3" width="44.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1080,1043 +1079,1043 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>19</v>
+    <row r="2" spans="1:4" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A3" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A4" s="3" t="s">
-        <v>23</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>142</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>25</v>
+        <v>110</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>26</v>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>27</v>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>28</v>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>117</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>30</v>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>128</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
-      <c r="A10" s="4" t="s">
-        <v>32</v>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>33</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>33</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>38</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="171" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:4" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="114" x14ac:dyDescent="0.45">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C14" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="99.75" x14ac:dyDescent="0.45">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>37</v>
+        <v>101</v>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="156.75" x14ac:dyDescent="0.45">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>38</v>
+        <v>115</v>
       </c>
       <c r="B16">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C16" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>39</v>
+        <v>125</v>
       </c>
       <c r="B17">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C17" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>40</v>
+        <v>135</v>
       </c>
       <c r="B18">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="128.25" x14ac:dyDescent="0.45">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C19" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="71.25" x14ac:dyDescent="0.45">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="B20">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C20" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="85.5" x14ac:dyDescent="0.45">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="B21">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C21" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="199.5" x14ac:dyDescent="0.45">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="B22">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C22" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B23">
+        <v>12</v>
+      </c>
+      <c r="C23" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="B23">
-        <v>5</v>
-      </c>
-      <c r="C23" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A24" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24">
-        <v>5</v>
-      </c>
-      <c r="C24" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="242.25" x14ac:dyDescent="0.45">
-      <c r="A25" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B25">
-        <v>5</v>
-      </c>
-      <c r="C25" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="156.75" x14ac:dyDescent="0.45">
-      <c r="A26" s="4" t="s">
-        <v>48</v>
       </c>
       <c r="B26">
         <v>5</v>
       </c>
       <c r="C26" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="128.25" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="B27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C27" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="99.75" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="B28">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C28" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="156.75" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="B29">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C29" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="171" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>53</v>
+        <v>120</v>
       </c>
       <c r="B30">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C30" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="185.25" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>54</v>
+        <v>131</v>
       </c>
       <c r="B31">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C31" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="99.75" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>55</v>
+        <v>132</v>
       </c>
       <c r="B32">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C32" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="128.25" x14ac:dyDescent="0.45">
-      <c r="A33" s="4" t="s">
-        <v>56</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="B33">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="71.25" x14ac:dyDescent="0.45">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C34" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B35">
         <v>10</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" ht="85.5" x14ac:dyDescent="0.45">
-      <c r="A35" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B35">
-        <v>6</v>
-      </c>
       <c r="C35" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="71.25" x14ac:dyDescent="0.45">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="B36">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="B37">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C37" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="85.5" x14ac:dyDescent="0.45">
-      <c r="A38" s="4" t="s">
-        <v>61</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>28</v>
       </c>
       <c r="B38">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="85.5" x14ac:dyDescent="0.45">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="B39">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C39" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="57" x14ac:dyDescent="0.45">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="B40">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C40" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="B41">
         <v>7</v>
       </c>
       <c r="C41" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="256.5" x14ac:dyDescent="0.45">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>67</v>
+        <v>113</v>
       </c>
       <c r="B42">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C42" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" ht="57" x14ac:dyDescent="0.45">
-      <c r="A43" s="4" t="s">
-        <v>68</v>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>26</v>
       </c>
       <c r="B43">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C43" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" ht="99.75" x14ac:dyDescent="0.45">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="B44">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C44" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" ht="128.25" x14ac:dyDescent="0.45">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="B45">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C45" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="85.5" x14ac:dyDescent="0.45">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="B46">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C46" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" ht="57" x14ac:dyDescent="0.45">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B47">
         <v>7</v>
       </c>
       <c r="C47" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" ht="114" x14ac:dyDescent="0.45">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="B48">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C48" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="B49">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C49" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" ht="99.75" x14ac:dyDescent="0.45">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="B50">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C50" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" ht="185.25" x14ac:dyDescent="0.45">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="B51">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C51" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" ht="142.5" x14ac:dyDescent="0.45">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="B52">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C52" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" ht="128.25" x14ac:dyDescent="0.45">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="B53">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C53" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="85.5" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="B54">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C54" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" ht="142.5" x14ac:dyDescent="0.45">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="B55">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C55" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="B56">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C56" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" ht="114" x14ac:dyDescent="0.45">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="B57">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C57" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" ht="114" x14ac:dyDescent="0.45">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="B58">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C58" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" ht="57" x14ac:dyDescent="0.45">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="B59">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C59" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" ht="171" x14ac:dyDescent="0.45">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B60">
         <v>8</v>
       </c>
       <c r="C60" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" ht="128.25" x14ac:dyDescent="0.45">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B61">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C61" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" ht="57" x14ac:dyDescent="0.45">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>89</v>
+        <v>134</v>
       </c>
       <c r="B62">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C62" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B63">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A63" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B63">
-        <v>8</v>
-      </c>
       <c r="C63" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="B64">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C64" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" ht="71.25" x14ac:dyDescent="0.45">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B65">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C65" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" ht="57" x14ac:dyDescent="0.45">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="B66">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C66" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B67">
+        <v>11</v>
+      </c>
+      <c r="C67" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="B67">
-        <v>9</v>
-      </c>
-      <c r="C67" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A68" s="4" t="s">
-        <v>95</v>
       </c>
       <c r="B68">
         <v>9</v>
       </c>
       <c r="C68" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="B69">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C69" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B70">
+        <v>11</v>
+      </c>
+      <c r="C70" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B71">
+        <v>13</v>
+      </c>
+      <c r="C71" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B72">
+        <v>2</v>
+      </c>
+      <c r="C72" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A70" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B70">
-        <v>9</v>
-      </c>
-      <c r="C70" t="s">
+    <row r="73" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B73">
+        <v>3</v>
+      </c>
+      <c r="C73" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B74">
         <v>4</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" ht="156.75" x14ac:dyDescent="0.45">
-      <c r="A71" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B71">
-        <v>10</v>
-      </c>
-      <c r="C71" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" ht="156.75" x14ac:dyDescent="0.45">
-      <c r="A72" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B72">
-        <v>10</v>
-      </c>
-      <c r="C72" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" ht="171" x14ac:dyDescent="0.45">
-      <c r="A73" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B73">
-        <v>10</v>
-      </c>
-      <c r="C73" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" ht="128.25" x14ac:dyDescent="0.45">
-      <c r="A74" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B74">
-        <v>10</v>
-      </c>
       <c r="C74" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" ht="57" x14ac:dyDescent="0.45">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>103</v>
+        <v>55</v>
       </c>
       <c r="B75">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C75" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="57" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>103</v>
+        <v>60</v>
       </c>
       <c r="B76">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C76" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="128.25" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>104</v>
+        <v>69</v>
       </c>
       <c r="B77">
+        <v>7</v>
+      </c>
+      <c r="C77" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B78">
+        <v>7</v>
+      </c>
+      <c r="C78" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B79">
+        <v>8</v>
+      </c>
+      <c r="C79" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B80">
+        <v>8</v>
+      </c>
+      <c r="C80" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B81">
+        <v>8</v>
+      </c>
+      <c r="C81" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B82">
+        <v>9</v>
+      </c>
+      <c r="C82" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B83">
         <v>10</v>
       </c>
-      <c r="C77" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" ht="85.5" x14ac:dyDescent="0.45">
-      <c r="A78" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="B78">
+      <c r="C83" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B84">
         <v>10</v>
       </c>
-      <c r="C78" t="s">
+      <c r="C84" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B85">
+        <v>11</v>
+      </c>
+      <c r="C85" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B86">
         <v>12</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" ht="142.5" x14ac:dyDescent="0.45">
-      <c r="A79" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B79">
-        <v>10</v>
-      </c>
-      <c r="C79" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A80" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="B80">
-        <v>10</v>
-      </c>
-      <c r="C80" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" ht="99.75" x14ac:dyDescent="0.45">
-      <c r="A81" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B81">
-        <v>10</v>
-      </c>
-      <c r="C81" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" ht="213.75" x14ac:dyDescent="0.45">
-      <c r="A82" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B82">
-        <v>11</v>
-      </c>
-      <c r="C82" t="s">
+      <c r="C86" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B87">
+        <v>12</v>
+      </c>
+      <c r="C87" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B88">
         <v>13</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" ht="199.5" x14ac:dyDescent="0.45">
-      <c r="A83" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B83">
-        <v>11</v>
-      </c>
-      <c r="C83" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" ht="114" x14ac:dyDescent="0.45">
-      <c r="A84" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B84">
-        <v>11</v>
-      </c>
-      <c r="C84" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" ht="299.25" x14ac:dyDescent="0.45">
-      <c r="A85" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B85">
-        <v>11</v>
-      </c>
-      <c r="C85" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" ht="114" x14ac:dyDescent="0.45">
-      <c r="A86" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B86">
-        <v>11</v>
-      </c>
-      <c r="C86" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" ht="256.5" x14ac:dyDescent="0.45">
-      <c r="A87" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B87">
-        <v>11</v>
-      </c>
-      <c r="C87" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" ht="213.75" x14ac:dyDescent="0.45">
-      <c r="A88" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B88">
-        <v>11</v>
       </c>
       <c r="C88" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="185.25" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="B89">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C89" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" ht="185.25" x14ac:dyDescent="0.45">
-      <c r="A90" s="4" t="s">
-        <v>119</v>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>27</v>
       </c>
       <c r="B90">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C90" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B91">
+        <v>9</v>
+      </c>
+      <c r="C91" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B92">
         <v>8</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" ht="128.25" x14ac:dyDescent="0.45">
-      <c r="A91" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B91">
-        <v>11</v>
-      </c>
-      <c r="C91" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" ht="99.75" x14ac:dyDescent="0.45">
-      <c r="A92" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B92">
-        <v>11</v>
-      </c>
       <c r="C92" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" ht="156.75" x14ac:dyDescent="0.45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="B93">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C93" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" ht="185.25" x14ac:dyDescent="0.45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>123</v>
+        <v>43</v>
       </c>
       <c r="B94">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C94" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" ht="171" x14ac:dyDescent="0.45">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B95">
+        <v>8</v>
+      </c>
+      <c r="C95" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="4" t="s">
         <v>124</v>
-      </c>
-      <c r="B95">
-        <v>11</v>
-      </c>
-      <c r="C95" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" ht="213.75" x14ac:dyDescent="0.45">
-      <c r="A96" s="4" t="s">
-        <v>125</v>
       </c>
       <c r="B96">
         <v>11</v>
@@ -2125,174 +2124,174 @@
         <v>6</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="57" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>126</v>
+        <v>49</v>
       </c>
       <c r="B97">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C97" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" ht="213.75" x14ac:dyDescent="0.45">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>127</v>
+        <v>67</v>
       </c>
       <c r="B98">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C98" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" ht="128.25" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="B99">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C99" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>129</v>
+        <v>82</v>
       </c>
       <c r="B100">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C100" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" ht="85.5" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="B101">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C101" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" ht="85.5" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="B102">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C102" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" ht="114" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="B103">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C103" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" ht="71.25" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>133</v>
+        <v>52</v>
       </c>
       <c r="B104">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C104" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="B105">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C105" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B106">
+        <v>5</v>
+      </c>
+      <c r="C106" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B107">
+        <v>8</v>
+      </c>
+      <c r="C107" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>30</v>
+      </c>
+      <c r="B108">
+        <v>1</v>
+      </c>
+      <c r="C108" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B109">
+        <v>5</v>
+      </c>
+      <c r="C109" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="4" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" ht="57" x14ac:dyDescent="0.45">
-      <c r="A106" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="B106">
-        <v>13</v>
-      </c>
-      <c r="C106" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" ht="128.25" x14ac:dyDescent="0.45">
-      <c r="A107" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="B107">
-        <v>13</v>
-      </c>
-      <c r="C107" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" ht="185.25" x14ac:dyDescent="0.45">
-      <c r="A108" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="B108">
-        <v>13</v>
-      </c>
-      <c r="C108" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" ht="114" x14ac:dyDescent="0.45">
-      <c r="A109" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="B109">
-        <v>13</v>
-      </c>
-      <c r="C109" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" ht="99.75" x14ac:dyDescent="0.45">
-      <c r="A110" s="4" t="s">
-        <v>140</v>
-      </c>
       <c r="B110">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C110" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" ht="199.5" x14ac:dyDescent="0.45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B111">
+        <v>11</v>
+      </c>
+      <c r="C111" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="4" t="s">
         <v>141</v>
-      </c>
-      <c r="B111">
-        <v>13</v>
-      </c>
-      <c r="C111" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" ht="156.75" x14ac:dyDescent="0.45">
-      <c r="A112" s="4" t="s">
-        <v>142</v>
       </c>
       <c r="B112">
         <v>13</v>
@@ -2301,72 +2300,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="113" spans="3:3" x14ac:dyDescent="0.45">
-      <c r="C113" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="114" spans="3:3" x14ac:dyDescent="0.45">
-      <c r="C114" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="115" spans="3:3" x14ac:dyDescent="0.45">
-      <c r="C115" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="116" spans="3:3" x14ac:dyDescent="0.45">
-      <c r="C116" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="117" spans="3:3" x14ac:dyDescent="0.45">
-      <c r="C117" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="118" spans="3:3" x14ac:dyDescent="0.45">
-      <c r="C118" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="119" spans="3:3" x14ac:dyDescent="0.45">
-      <c r="C119" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="120" spans="3:3" x14ac:dyDescent="0.45">
-      <c r="C120" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="121" spans="3:3" x14ac:dyDescent="0.45">
-      <c r="C121" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="122" spans="3:3" x14ac:dyDescent="0.45">
-      <c r="C122" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="123" spans="3:3" x14ac:dyDescent="0.45">
-      <c r="C123" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="124" spans="3:3" x14ac:dyDescent="0.45">
-      <c r="C124" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="125" spans="3:3" x14ac:dyDescent="0.45">
-      <c r="C125" t="s">
-        <v>11</v>
-      </c>
-    </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D112">
+    <sortCondition ref="C1:C112"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -2392,149 +2329,149 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29CB02DE-B6DC-4E34-9F59-3C6217DF06D7}">
   <dimension ref="A1:A28"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="58.9296875" customWidth="1"/>
+    <col min="1" max="1" width="59" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.45">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.45">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.45">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/data/transcripts/Int_Codes.xlsx
+++ b/data/transcripts/Int_Codes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JoeWe\Uni\IndProject\Project\data\transcripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA10CB26-2F83-491B-B702-38D0FA2733AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D6AC11-F82B-4DE6-84AD-958D82599DCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="150">
   <si>
     <t>Quote</t>
   </si>
@@ -611,13 +611,6 @@
 So that is more than enough, I feel like.</t>
   </si>
   <si>
-    <t>So I should be just, just like a small part of the, your vision in the glasses, just like a little bit notification. On the on the left or the right.
-Oh, yeah. Where it's coming.
-If the person is calling you from the left side, I just might want to take this.
-Yeah, yeah, yeah.
-A little like icon or something.</t>
-  </si>
-  <si>
     <t>But I don't think this might work because it's gonna be, it's not gonna detect your name.
 Yeah, or yeah, if it, if it could, that, that's, like, best scenario.
 Yeah.
@@ -718,6 +711,49 @@
   <si>
     <t>So, I think it's because I'm more familiar with the radar.
 So, like, in video games, they use the radar, so, yeah, and I play a lot of video games, so I'm more familiar with it.</t>
+  </si>
+  <si>
+    <t>So I should be just, just like a small part of the, your vision in the glasses, just like a little bit notification. On the on the left or the right where it's coming from. If the person is calling you from the left side, I just might want a little like icon or something.</t>
+  </si>
+  <si>
+    <t>I think lights could be useful if you're very close.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">you'd want to know about vehicles nearby?
+Anything that could crush you?
+And you probably want to know when people are talking at least talking at you.
+</t>
+  </si>
+  <si>
+    <t>Or just in general, yeah, there are multiple sounds going on around you.
+How would the system deal with that?
+Would there be multiple arrows?
+Would there be different coloured lights?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I I, I think sounds shouldn't be displayed as in.
+Relative to where you're standing is in an arrow coming from where you are towards it.
+It would make more sense for the visual bit to be where the sound is or at least where the microphone thinks the sound is.
+So for example, if it was like over there, there'd maybe be a little circle emitting.
+To show me there's a sound over there.
+And then, maybe if I'm not looking at it, then I could get an arrow or bleat to show me that there's something behind me.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+I mean, I suppose, yeah, something to represent the distance and you'd also want to represent what it actually is.
+For example, if you were wearing it, a plane went over your head.
+The arrow would be facing far away from you and then pass over you.
+Which might make you think you're on top of the sound, but the sound's already going way behind you because the plane's just passed over.
+So you'd want some way of knowing that is what the sound was.</t>
+  </si>
+  <si>
+    <t>There'd be multiple sounds and if you were moving at the same time, the sound is moving.
+That's something that wasn't in the experiment and that could potentially be very confusing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I think it would create a bigger impairment than not using it andit would be too distracting to be worth it
+</t>
   </si>
 </sst>
 </file>
@@ -1057,7 +1093,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D112"/>
+  <dimension ref="A1:D119"/>
   <sheetFormatPr defaultRowHeight="93" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51" customWidth="1"/>
@@ -1103,7 +1139,7 @@
     </row>
     <row r="4" spans="1:4" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B4">
         <v>9</v>
@@ -1158,7 +1194,7 @@
     </row>
     <row r="9" spans="1:4" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B9">
         <v>12</v>
@@ -1246,7 +1282,7 @@
     </row>
     <row r="17" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B17">
         <v>12</v>
@@ -1257,7 +1293,7 @@
     </row>
     <row r="18" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B18">
         <v>13</v>
@@ -1312,7 +1348,7 @@
     </row>
     <row r="23" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B23">
         <v>12</v>
@@ -1400,7 +1436,7 @@
     </row>
     <row r="31" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B31">
         <v>13</v>
@@ -1411,7 +1447,7 @@
     </row>
     <row r="32" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B32">
         <v>13</v>
@@ -1620,7 +1656,7 @@
     </row>
     <row r="51" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B51">
         <v>12</v>
@@ -1631,7 +1667,7 @@
     </row>
     <row r="52" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B52">
         <v>13</v>
@@ -1741,7 +1777,7 @@
     </row>
     <row r="62" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B62">
         <v>13</v>
@@ -1840,7 +1876,7 @@
     </row>
     <row r="71" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B71">
         <v>13</v>
@@ -2005,7 +2041,7 @@
     </row>
     <row r="86" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B86">
         <v>12</v>
@@ -2016,7 +2052,7 @@
     </row>
     <row r="87" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B87">
         <v>12</v>
@@ -2027,7 +2063,7 @@
     </row>
     <row r="88" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B88">
         <v>13</v>
@@ -2038,7 +2074,7 @@
     </row>
     <row r="89" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B89">
         <v>13</v>
@@ -2082,7 +2118,7 @@
     </row>
     <row r="93" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B93">
         <v>13</v>
@@ -2115,7 +2151,7 @@
     </row>
     <row r="96" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B96">
         <v>11</v>
@@ -2280,7 +2316,7 @@
     </row>
     <row r="111" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="B111">
         <v>11</v>
@@ -2291,13 +2327,90 @@
     </row>
     <row r="112" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B112">
         <v>13</v>
       </c>
       <c r="C112" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B113">
+        <v>14</v>
+      </c>
+      <c r="C113" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B114">
+        <v>14</v>
+      </c>
+      <c r="C114" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B115">
+        <v>14</v>
+      </c>
+      <c r="C115" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B116">
+        <v>14</v>
+      </c>
+      <c r="C116" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B117">
+        <v>14</v>
+      </c>
+      <c r="C117" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B118">
+        <v>14</v>
+      </c>
+      <c r="C118" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B119">
+        <v>14</v>
+      </c>
+      <c r="C119" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -2471,7 +2584,7 @@
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
